--- a/backend/data/financials_by_company/002137.SZ.xlsx
+++ b/backend/data/financials_by_company/002137.SZ.xlsx
@@ -682,634 +682,634 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-15439996.7825</v>
+        <v>-32665199.4925</v>
       </c>
       <c r="C2" t="n">
         <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>82613355.94</v>
+        <v>49277510.27</v>
       </c>
       <c r="E2" t="n">
-        <v>-61759987.13</v>
+        <v>-130660797.97</v>
       </c>
       <c r="F2" t="n">
-        <v>-61759987.13</v>
+        <v>-130660797.97</v>
       </c>
       <c r="G2" t="n">
-        <v>-23407520.67</v>
+        <v>-95330409.22</v>
       </c>
       <c r="H2" t="n">
-        <v>24545705.41</v>
+        <v>18670053.52</v>
       </c>
       <c r="I2" t="n">
-        <v>466730494.54</v>
+        <v>780240294.92</v>
       </c>
       <c r="J2" t="n">
-        <v>20853368.81</v>
+        <v>-81383287.7</v>
       </c>
       <c r="K2" t="n">
-        <v>-3692336.6</v>
+        <v>-100053341.22</v>
       </c>
       <c r="L2" t="n">
-        <v>-264804.33</v>
+        <v>439533.45</v>
       </c>
       <c r="M2" t="n">
-        <v>329808.31</v>
+        <v>414108.99</v>
       </c>
       <c r="N2" t="n">
-        <v>1081368.26</v>
+        <v>1113709.69</v>
       </c>
       <c r="O2" t="n">
-        <v>22912469.6775</v>
+        <v>2665189.2575</v>
       </c>
       <c r="P2" t="n">
-        <v>-23407520.67</v>
+        <v>-95330409.22</v>
       </c>
       <c r="Q2" t="n">
-        <v>560063345.98</v>
+        <v>902315278.62</v>
       </c>
       <c r="R2" t="n">
-        <v>-5881359.09</v>
+        <v>-97012754.59999999</v>
       </c>
       <c r="S2" t="n">
-        <v>577963473</v>
+        <v>577410110</v>
       </c>
       <c r="T2" t="n">
-        <v>577963473</v>
+        <v>577410110</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0405</v>
+        <v>-0.1651</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0405</v>
+        <v>-0.1651</v>
       </c>
       <c r="W2" t="n">
-        <v>-23407520.67</v>
+        <v>-95330409.22</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-23407520.67</v>
+        <v>-95330409.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>-12611347.18</v>
+        <v>11920284.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>-10796173.49</v>
+        <v>-107250693.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>-10796173.49</v>
+        <v>-107250693.62</v>
       </c>
       <c r="AC2" t="n">
-        <v>6774028.58</v>
+        <v>6783243.41</v>
       </c>
       <c r="AD2" t="n">
-        <v>-4022144.91</v>
+        <v>-100467450.21</v>
       </c>
       <c r="AE2" t="n">
-        <v>2610774.13</v>
+        <v>-3381508.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>-11485083</v>
+        <v>-148528034.69</v>
       </c>
       <c r="AG2" t="n">
-        <v>476364.54</v>
+        <v>654196.17</v>
       </c>
       <c r="AH2" t="n">
-        <v>1480550.67</v>
+        <v>14177541.39</v>
       </c>
       <c r="AI2" t="n">
-        <v>9528167.789999999</v>
+        <v>133696297.13</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-264804.33</v>
+        <v>439533.45</v>
       </c>
       <c r="AK2" t="n">
-        <v>1016364.28</v>
+        <v>260067.25</v>
       </c>
       <c r="AL2" t="n">
-        <v>329808.31</v>
+        <v>414108.99</v>
       </c>
       <c r="AM2" t="n">
-        <v>1081368.26</v>
+        <v>1113709.69</v>
       </c>
       <c r="AN2" t="n">
-        <v>34681631.49</v>
+        <v>19054020.24</v>
       </c>
       <c r="AO2" t="n">
-        <v>93332851.44</v>
+        <v>122074983.7</v>
       </c>
       <c r="AP2" t="n">
-        <v>4564690.72</v>
+        <v>4209726.47</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9443214</v>
+        <v>5516187.25</v>
       </c>
       <c r="AR2" t="n">
-        <v>9443214</v>
+        <v>5516187.25</v>
       </c>
       <c r="AS2" t="n">
-        <v>35166588.81</v>
+        <v>51934210.13</v>
       </c>
       <c r="AT2" t="n">
-        <v>16605175.46</v>
+        <v>22754585.61</v>
       </c>
       <c r="AU2" t="n">
-        <v>7823613.01</v>
+        <v>6343529.13</v>
       </c>
       <c r="AV2" t="n">
-        <v>8781562.449999999</v>
+        <v>16411056.48</v>
       </c>
       <c r="AW2" t="n">
-        <v>128014482.93</v>
+        <v>141129003.94</v>
       </c>
       <c r="AX2" t="n">
-        <v>466730494.54</v>
+        <v>780240294.92</v>
       </c>
       <c r="AY2" t="n">
-        <v>594744977.47</v>
+        <v>921369298.86</v>
       </c>
       <c r="AZ2" t="n">
-        <v>594744977.47</v>
+        <v>921369298.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-12615616.5975</v>
+        <v>5912688.612516</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25</v>
+        <v>0.081801</v>
       </c>
       <c r="D3" t="n">
-        <v>63985606.32</v>
+        <v>105484042.48</v>
       </c>
       <c r="E3" t="n">
-        <v>-50462466.39</v>
+        <v>72281645.33</v>
       </c>
       <c r="F3" t="n">
-        <v>-50462466.39</v>
+        <v>72281645.33</v>
       </c>
       <c r="G3" t="n">
-        <v>10458696.68</v>
+        <v>144194342.25</v>
       </c>
       <c r="H3" t="n">
-        <v>15867382.19</v>
+        <v>15974826.5</v>
       </c>
       <c r="I3" t="n">
-        <v>465513429.17</v>
+        <v>495603739.66</v>
       </c>
       <c r="J3" t="n">
-        <v>13523139.93</v>
+        <v>177765687.81</v>
       </c>
       <c r="K3" t="n">
-        <v>-2344242.26</v>
+        <v>161790861.31</v>
       </c>
       <c r="L3" t="n">
-        <v>-271047.63</v>
+        <v>347025.5</v>
       </c>
       <c r="M3" t="n">
-        <v>322060.93</v>
+        <v>338919.59</v>
       </c>
       <c r="N3" t="n">
-        <v>1217808.96</v>
+        <v>915807.0600000001</v>
       </c>
       <c r="O3" t="n">
-        <v>48305546.4725</v>
+        <v>77825385.532516</v>
       </c>
       <c r="P3" t="n">
-        <v>10458696.68</v>
+        <v>144194342.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>559004893.83</v>
+        <v>598377760.48</v>
       </c>
       <c r="R3" t="n">
-        <v>-1935739.58</v>
+        <v>132900161.78</v>
       </c>
       <c r="S3" t="n">
-        <v>577828546</v>
+        <v>577470333</v>
       </c>
       <c r="T3" t="n">
-        <v>577828546</v>
+        <v>577470333</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0181</v>
+        <v>0.2497</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0181</v>
+        <v>0.2497</v>
       </c>
       <c r="W3" t="n">
-        <v>10458696.68</v>
+        <v>144194342.25</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>10458696.68</v>
+        <v>144194342.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>-8143068</v>
+        <v>-4050718.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>18601764.68</v>
+        <v>148245061.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>18601764.68</v>
+        <v>148245061.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>-21268067.87</v>
+        <v>13206880.57</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2666303.19</v>
+        <v>161451941.72</v>
       </c>
       <c r="AE3" t="n">
-        <v>142682.98</v>
+        <v>28269946.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>-5671415.06</v>
+        <v>88757155.72</v>
       </c>
       <c r="AG3" t="n">
-        <v>47854.08</v>
+        <v>-102733746.71</v>
       </c>
       <c r="AH3" t="n">
-        <v>-3343946.64</v>
+        <v>4936763.97</v>
       </c>
       <c r="AI3" t="n">
-        <v>8967507.619999999</v>
+        <v>9039827.02</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-271047.63</v>
+        <v>347025.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>1166795.66</v>
+        <v>229861.97</v>
       </c>
       <c r="AL3" t="n">
-        <v>322060.93</v>
+        <v>338919.59</v>
       </c>
       <c r="AM3" t="n">
-        <v>1217808.96</v>
+        <v>915807.0600000001</v>
       </c>
       <c r="AN3" t="n">
-        <v>35325218.38</v>
+        <v>39896182.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>93491464.66</v>
+        <v>102774020.82</v>
       </c>
       <c r="AP3" t="n">
-        <v>3719300.41</v>
+        <v>3295576.19</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1522752.98</v>
+        <v>4176342.61</v>
       </c>
       <c r="AR3" t="n">
-        <v>1522752.98</v>
+        <v>4176342.61</v>
       </c>
       <c r="AS3" t="n">
-        <v>41528016.07</v>
+        <v>38008850.33</v>
       </c>
       <c r="AT3" t="n">
-        <v>18785028.69</v>
+        <v>18547410.67</v>
       </c>
       <c r="AU3" t="n">
-        <v>6840133.46</v>
+        <v>6324031.81</v>
       </c>
       <c r="AV3" t="n">
-        <v>11944895.23</v>
+        <v>12223378.86</v>
       </c>
       <c r="AW3" t="n">
-        <v>128816683.04</v>
+        <v>142670203.32</v>
       </c>
       <c r="AX3" t="n">
-        <v>465513429.17</v>
+        <v>495603739.66</v>
       </c>
       <c r="AY3" t="n">
-        <v>594330112.21</v>
+        <v>638273942.98</v>
       </c>
       <c r="AZ3" t="n">
-        <v>594330112.21</v>
+        <v>638273942.98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>5912688.612516</v>
+        <v>-12615616.5975</v>
       </c>
       <c r="C4" t="n">
-        <v>0.081801</v>
+        <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>105484042.48</v>
+        <v>63985606.32</v>
       </c>
       <c r="E4" t="n">
-        <v>72281645.33</v>
+        <v>-50462466.39</v>
       </c>
       <c r="F4" t="n">
-        <v>72281645.33</v>
+        <v>-50462466.39</v>
       </c>
       <c r="G4" t="n">
-        <v>144194342.25</v>
+        <v>10458696.68</v>
       </c>
       <c r="H4" t="n">
-        <v>15974826.5</v>
+        <v>15867382.19</v>
       </c>
       <c r="I4" t="n">
-        <v>495603739.66</v>
+        <v>465513429.17</v>
       </c>
       <c r="J4" t="n">
-        <v>177765687.81</v>
+        <v>13523139.93</v>
       </c>
       <c r="K4" t="n">
-        <v>161790861.31</v>
+        <v>-2344242.26</v>
       </c>
       <c r="L4" t="n">
-        <v>347025.5</v>
+        <v>-271047.63</v>
       </c>
       <c r="M4" t="n">
-        <v>338919.59</v>
+        <v>322060.93</v>
       </c>
       <c r="N4" t="n">
-        <v>915807.0600000001</v>
+        <v>1217808.96</v>
       </c>
       <c r="O4" t="n">
-        <v>77825385.532516</v>
+        <v>48305546.4725</v>
       </c>
       <c r="P4" t="n">
-        <v>144194342.25</v>
+        <v>10458696.68</v>
       </c>
       <c r="Q4" t="n">
-        <v>598377760.48</v>
+        <v>559004893.83</v>
       </c>
       <c r="R4" t="n">
-        <v>132900161.78</v>
+        <v>-1935739.58</v>
       </c>
       <c r="S4" t="n">
-        <v>577470333</v>
+        <v>577828546</v>
       </c>
       <c r="T4" t="n">
-        <v>577470333</v>
+        <v>577828546</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2497</v>
+        <v>0.0181</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2497</v>
+        <v>0.0181</v>
       </c>
       <c r="W4" t="n">
-        <v>144194342.25</v>
+        <v>10458696.68</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>144194342.25</v>
+        <v>10458696.68</v>
       </c>
       <c r="Z4" t="n">
-        <v>-4050718.9</v>
+        <v>-8143068</v>
       </c>
       <c r="AA4" t="n">
-        <v>148245061.15</v>
+        <v>18601764.68</v>
       </c>
       <c r="AB4" t="n">
-        <v>148245061.15</v>
+        <v>18601764.68</v>
       </c>
       <c r="AC4" t="n">
-        <v>13206880.57</v>
+        <v>-21268067.87</v>
       </c>
       <c r="AD4" t="n">
-        <v>161451941.72</v>
+        <v>-2666303.19</v>
       </c>
       <c r="AE4" t="n">
-        <v>28269946.1</v>
+        <v>142682.98</v>
       </c>
       <c r="AF4" t="n">
-        <v>88757155.72</v>
+        <v>-5671415.06</v>
       </c>
       <c r="AG4" t="n">
-        <v>-102733746.71</v>
+        <v>47854.08</v>
       </c>
       <c r="AH4" t="n">
-        <v>4936763.97</v>
+        <v>-3343946.64</v>
       </c>
       <c r="AI4" t="n">
-        <v>9039827.02</v>
+        <v>8967507.619999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>347025.5</v>
+        <v>-271047.63</v>
       </c>
       <c r="AK4" t="n">
-        <v>229861.97</v>
+        <v>1166795.66</v>
       </c>
       <c r="AL4" t="n">
-        <v>338919.59</v>
+        <v>322060.93</v>
       </c>
       <c r="AM4" t="n">
-        <v>915807.0600000001</v>
+        <v>1217808.96</v>
       </c>
       <c r="AN4" t="n">
-        <v>39896182.5</v>
+        <v>35325218.38</v>
       </c>
       <c r="AO4" t="n">
-        <v>102774020.82</v>
+        <v>93491464.66</v>
       </c>
       <c r="AP4" t="n">
-        <v>3295576.19</v>
+        <v>3719300.41</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4176342.61</v>
+        <v>1522752.98</v>
       </c>
       <c r="AR4" t="n">
-        <v>4176342.61</v>
+        <v>1522752.98</v>
       </c>
       <c r="AS4" t="n">
-        <v>38008850.33</v>
+        <v>41528016.07</v>
       </c>
       <c r="AT4" t="n">
-        <v>18547410.67</v>
+        <v>18785028.69</v>
       </c>
       <c r="AU4" t="n">
-        <v>6324031.81</v>
+        <v>6840133.46</v>
       </c>
       <c r="AV4" t="n">
-        <v>12223378.86</v>
+        <v>11944895.23</v>
       </c>
       <c r="AW4" t="n">
-        <v>142670203.32</v>
+        <v>128816683.04</v>
       </c>
       <c r="AX4" t="n">
-        <v>495603739.66</v>
+        <v>465513429.17</v>
       </c>
       <c r="AY4" t="n">
-        <v>638273942.98</v>
+        <v>594330112.21</v>
       </c>
       <c r="AZ4" t="n">
-        <v>638273942.98</v>
+        <v>594330112.21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-32665199.4925</v>
+        <v>-15439996.7825</v>
       </c>
       <c r="C5" t="n">
         <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>49277510.27</v>
+        <v>82613355.94</v>
       </c>
       <c r="E5" t="n">
-        <v>-130660797.97</v>
+        <v>-61759987.13</v>
       </c>
       <c r="F5" t="n">
-        <v>-130660797.97</v>
+        <v>-61759987.13</v>
       </c>
       <c r="G5" t="n">
-        <v>-95330409.22</v>
+        <v>-23407520.67</v>
       </c>
       <c r="H5" t="n">
-        <v>18670053.52</v>
+        <v>24545705.41</v>
       </c>
       <c r="I5" t="n">
-        <v>780240294.92</v>
+        <v>466730494.54</v>
       </c>
       <c r="J5" t="n">
-        <v>-81383287.7</v>
+        <v>20853368.81</v>
       </c>
       <c r="K5" t="n">
-        <v>-100053341.22</v>
+        <v>-3692336.6</v>
       </c>
       <c r="L5" t="n">
-        <v>439533.45</v>
+        <v>-264804.33</v>
       </c>
       <c r="M5" t="n">
-        <v>414108.99</v>
+        <v>329808.31</v>
       </c>
       <c r="N5" t="n">
-        <v>1113709.69</v>
+        <v>1081368.26</v>
       </c>
       <c r="O5" t="n">
-        <v>2665189.2575</v>
+        <v>22912469.6775</v>
       </c>
       <c r="P5" t="n">
-        <v>-95330409.22</v>
+        <v>-23407520.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>902315278.62</v>
+        <v>560063345.98</v>
       </c>
       <c r="R5" t="n">
-        <v>-97012754.59999999</v>
+        <v>-5881359.09</v>
       </c>
       <c r="S5" t="n">
-        <v>577410110</v>
+        <v>577963473</v>
       </c>
       <c r="T5" t="n">
-        <v>577410110</v>
+        <v>577963473</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1651</v>
+        <v>-0.0405</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1651</v>
+        <v>-0.0405</v>
       </c>
       <c r="W5" t="n">
-        <v>-95330409.22</v>
+        <v>-23407520.67</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-95330409.22</v>
+        <v>-23407520.67</v>
       </c>
       <c r="Z5" t="n">
-        <v>11920284.4</v>
+        <v>-12611347.18</v>
       </c>
       <c r="AA5" t="n">
-        <v>-107250693.62</v>
+        <v>-10796173.49</v>
       </c>
       <c r="AB5" t="n">
-        <v>-107250693.62</v>
+        <v>-10796173.49</v>
       </c>
       <c r="AC5" t="n">
-        <v>6783243.41</v>
+        <v>6774028.58</v>
       </c>
       <c r="AD5" t="n">
-        <v>-100467450.21</v>
+        <v>-4022144.91</v>
       </c>
       <c r="AE5" t="n">
-        <v>-3381508.3</v>
+        <v>2610774.13</v>
       </c>
       <c r="AF5" t="n">
-        <v>-148528034.69</v>
+        <v>-11485083</v>
       </c>
       <c r="AG5" t="n">
-        <v>654196.17</v>
+        <v>476364.54</v>
       </c>
       <c r="AH5" t="n">
-        <v>14177541.39</v>
+        <v>1480550.67</v>
       </c>
       <c r="AI5" t="n">
-        <v>133696297.13</v>
+        <v>9528167.789999999</v>
       </c>
       <c r="AJ5" t="n">
-        <v>439533.45</v>
+        <v>-264804.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>260067.25</v>
+        <v>1016364.28</v>
       </c>
       <c r="AL5" t="n">
-        <v>414108.99</v>
+        <v>329808.31</v>
       </c>
       <c r="AM5" t="n">
-        <v>1113709.69</v>
+        <v>1081368.26</v>
       </c>
       <c r="AN5" t="n">
-        <v>19054020.24</v>
+        <v>34681631.49</v>
       </c>
       <c r="AO5" t="n">
-        <v>122074983.7</v>
+        <v>93332851.44</v>
       </c>
       <c r="AP5" t="n">
-        <v>4209726.47</v>
+        <v>4564690.72</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5516187.25</v>
+        <v>9443214</v>
       </c>
       <c r="AR5" t="n">
-        <v>5516187.25</v>
+        <v>9443214</v>
       </c>
       <c r="AS5" t="n">
-        <v>51934210.13</v>
+        <v>35166588.81</v>
       </c>
       <c r="AT5" t="n">
-        <v>22754585.61</v>
+        <v>16605175.46</v>
       </c>
       <c r="AU5" t="n">
-        <v>6343529.13</v>
+        <v>7823613.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>16411056.48</v>
+        <v>8781562.449999999</v>
       </c>
       <c r="AW5" t="n">
-        <v>141129003.94</v>
+        <v>128014482.93</v>
       </c>
       <c r="AX5" t="n">
-        <v>780240294.92</v>
+        <v>466730494.54</v>
       </c>
       <c r="AY5" t="n">
-        <v>921369298.86</v>
+        <v>594744977.47</v>
       </c>
       <c r="AZ5" t="n">
-        <v>921369298.86</v>
+        <v>594744977.47</v>
       </c>
     </row>
   </sheetData>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>577504854</v>
@@ -1689,40 +1689,40 @@
         <v>577504854</v>
       </c>
       <c r="D2" t="n">
-        <v>6518126.54</v>
+        <v>8567861.630000001</v>
       </c>
       <c r="E2" t="n">
-        <v>1451251195.93</v>
+        <v>1323557533.39</v>
       </c>
       <c r="F2" t="n">
-        <v>1486291088.47</v>
+        <v>1356556272.29</v>
       </c>
       <c r="G2" t="n">
-        <v>320584113.02</v>
+        <v>607980141.99</v>
       </c>
       <c r="H2" t="n">
-        <v>1451251195.93</v>
+        <v>1323557533.39</v>
       </c>
       <c r="I2" t="n">
-        <v>177974.22</v>
+        <v>3578802.32</v>
       </c>
       <c r="J2" t="n">
-        <v>1481783534.47</v>
+        <v>1356556272.29</v>
       </c>
       <c r="K2" t="n">
-        <v>1484188778.47</v>
+        <v>1356556272.29</v>
       </c>
       <c r="L2" t="n">
-        <v>1545000026.89</v>
+        <v>1404564493.35</v>
       </c>
       <c r="M2" t="n">
-        <v>63216492.42</v>
+        <v>48008221.06</v>
       </c>
       <c r="N2" t="n">
-        <v>1481783534.47</v>
+        <v>1356556272.29</v>
       </c>
       <c r="O2" t="n">
-        <v>-74170568.37</v>
+        <v>-206525100.98</v>
       </c>
       <c r="P2" t="n">
         <v>870480939.47</v>
@@ -1734,164 +1734,162 @@
         <v>577504854</v>
       </c>
       <c r="S2" t="n">
-        <v>402605396.75</v>
+        <v>560587861.01</v>
       </c>
       <c r="T2" t="n">
-        <v>29762337.91</v>
+        <v>59367964.75</v>
       </c>
       <c r="U2" t="n">
-        <v>8414035.960000001</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1650000</v>
-      </c>
+        <v>8694378.619999999</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>5077895.49</v>
+        <v>261095.9</v>
       </c>
       <c r="X2" t="n">
-        <v>12037188.24</v>
+        <v>46833687.91</v>
       </c>
       <c r="Y2" t="n">
-        <v>2583218.22</v>
+        <v>3578802.32</v>
       </c>
       <c r="Z2" t="n">
-        <v>177974.22</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2405244</v>
-      </c>
+        <v>3578802.32</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>372843058.84</v>
+        <v>501219896.26</v>
       </c>
       <c r="AC2" t="n">
-        <v>11274582.29</v>
+        <v>7329208.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>3934908.32</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2102310</v>
-      </c>
+        <v>4989059.31</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>337569658.17</v>
+        <v>468732152.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>38912792.53</v>
+        <v>81110662.29000001</v>
       </c>
       <c r="AH2" t="n">
-        <v>11353330.38</v>
+        <v>8759974.140000001</v>
       </c>
       <c r="AI2" t="n">
-        <v>287303535.26</v>
+        <v>378861516.07</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1947605423.64</v>
+        <v>1965152354.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>1254178251.78</v>
+        <v>855952316.11</v>
       </c>
       <c r="AL2" t="n">
-        <v>849847.24</v>
+        <v>6930322.87</v>
       </c>
       <c r="AM2" t="n">
-        <v>14633669.92</v>
+        <v>1234562.3</v>
       </c>
       <c r="AN2" t="n">
-        <v>16325761.58</v>
+        <v>15178492.15</v>
       </c>
       <c r="AO2" t="n">
-        <v>941785908.6900001</v>
+        <v>687169793.16</v>
       </c>
       <c r="AP2" t="n">
-        <v>482893150.55</v>
+        <v>30011671.23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>458892758.14</v>
+        <v>657158121.9299999</v>
       </c>
       <c r="AR2" t="n">
-        <v>82244.77</v>
+        <v>3533649.11</v>
       </c>
       <c r="AS2" t="n">
-        <v>30532338.54</v>
+        <v>32998738.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>30532338.54</v>
+        <v>32998738.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>249968481.04</v>
+        <v>108906757.62</v>
       </c>
       <c r="AV2" t="n">
-        <v>-121012061.14</v>
+        <v>-122798140.93</v>
       </c>
       <c r="AW2" t="n">
-        <v>370980542.18</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+        <v>231704898.55</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>286359.26</v>
+      </c>
       <c r="AY2" t="n">
-        <v>29990239.01</v>
+        <v>23591194.67</v>
       </c>
       <c r="AZ2" t="n">
-        <v>125978795.42</v>
+        <v>105873602.98</v>
       </c>
       <c r="BA2" t="n">
-        <v>215011507.75</v>
+        <v>101953741.64</v>
       </c>
       <c r="BB2" t="n">
-        <v>693427171.86</v>
+        <v>1109200038.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>77280110.70999999</v>
-      </c>
-      <c r="BD2" t="inlineStr"/>
+        <v>263840614</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>23458626.11</v>
+      </c>
       <c r="BE2" t="n">
-        <v>1662545.88</v>
+        <v>7688880.78</v>
       </c>
       <c r="BF2" t="n">
-        <v>139278999.81</v>
+        <v>140298141.54</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
       <c r="BH2" t="n">
-        <v>56996654.38</v>
+        <v>17658563.15</v>
       </c>
       <c r="BI2" t="n">
-        <v>48741070.27</v>
+        <v>39437015.51</v>
       </c>
       <c r="BJ2" t="n">
-        <v>33541275.16</v>
+        <v>83202562.88</v>
       </c>
       <c r="BK2" t="n">
-        <v>26733639.97</v>
+        <v>11236877.54</v>
       </c>
       <c r="BL2" t="n">
-        <v>186622613.68</v>
+        <v>225519002.53</v>
       </c>
       <c r="BM2" t="n">
-        <v>-6682506.89</v>
+        <v>-41592316.05</v>
       </c>
       <c r="BN2" t="n">
-        <v>193305120.57</v>
+        <v>267111318.58</v>
       </c>
       <c r="BO2" t="n">
-        <v>261849261.81</v>
+        <v>437157895.75</v>
       </c>
       <c r="BP2" t="n">
-        <v>135692546.92</v>
+        <v>300311075.1</v>
       </c>
       <c r="BQ2" t="n">
-        <v>126156714.89</v>
+        <v>136846820.65</v>
       </c>
       <c r="BR2" t="n">
-        <v>30958920.4</v>
+        <v>43783872.28</v>
       </c>
       <c r="BS2" t="n">
-        <v>95197794.48999999</v>
+        <v>93062948.37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>577504854</v>
@@ -1900,40 +1898,40 @@
         <v>577504854</v>
       </c>
       <c r="D3" t="n">
-        <v>10873332.18</v>
+        <v>5339702.31</v>
       </c>
       <c r="E3" t="n">
-        <v>1479531427.47</v>
+        <v>1469166030.48</v>
       </c>
       <c r="F3" t="n">
-        <v>1516675822.86</v>
+        <v>1503077830.63</v>
       </c>
       <c r="G3" t="n">
-        <v>441901671.27</v>
+        <v>644139975.55</v>
       </c>
       <c r="H3" t="n">
-        <v>1479531427.47</v>
+        <v>1469166030.48</v>
       </c>
       <c r="I3" t="n">
-        <v>2644256.88</v>
+        <v>1327387.84</v>
       </c>
       <c r="J3" t="n">
-        <v>1510667563.67</v>
+        <v>1501065061.23</v>
       </c>
       <c r="K3" t="n">
-        <v>1513672018.67</v>
+        <v>1501065061.23</v>
       </c>
       <c r="L3" t="n">
-        <v>1563102181.11</v>
+        <v>1552257591.29</v>
       </c>
       <c r="M3" t="n">
-        <v>52434617.44</v>
+        <v>51192530.06</v>
       </c>
       <c r="N3" t="n">
-        <v>1510667563.67</v>
+        <v>1501065061.23</v>
       </c>
       <c r="O3" t="n">
-        <v>-51872062.05</v>
+        <v>-62330758.73</v>
       </c>
       <c r="P3" t="n">
         <v>870480939.47</v>
@@ -1945,164 +1943,162 @@
         <v>577504854</v>
       </c>
       <c r="S3" t="n">
-        <v>328590770.32</v>
+        <v>384296431.11</v>
       </c>
       <c r="T3" t="n">
-        <v>31024647.22</v>
+        <v>36254576.71</v>
       </c>
       <c r="U3" t="n">
-        <v>8388369.95</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1650000</v>
-      </c>
+        <v>3027604.25</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>3226545.76</v>
+        <v>219222.38</v>
       </c>
       <c r="X3" t="n">
-        <v>12111019.63</v>
+        <v>31680362.24</v>
       </c>
       <c r="Y3" t="n">
-        <v>5648711.88</v>
+        <v>1327387.84</v>
       </c>
       <c r="Z3" t="n">
-        <v>2644256.88</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3004455</v>
-      </c>
+        <v>1327387.84</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>297566123.1</v>
+        <v>348041854.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>4275212.18</v>
+        <v>4090508.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>5224620.3</v>
+        <v>4012314.47</v>
       </c>
       <c r="AE3" t="n">
-        <v>3003804.19</v>
+        <v>2012769.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>281375338.03</v>
+        <v>331116377.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>36708620.24</v>
+        <v>76955174.40000001</v>
       </c>
       <c r="AH3" t="n">
-        <v>8296307.17</v>
+        <v>22951473.67</v>
       </c>
       <c r="AI3" t="n">
-        <v>236370410.62</v>
+        <v>231209729.18</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1891692951.43</v>
+        <v>1936554022.4</v>
       </c>
       <c r="AK3" t="n">
-        <v>1152225157.06</v>
+        <v>944372192.45</v>
       </c>
       <c r="AL3" t="n">
-        <v>5056339.93</v>
+        <v>1932854.92</v>
       </c>
       <c r="AM3" t="n">
-        <v>16676008.56</v>
+        <v>8373593.47</v>
       </c>
       <c r="AN3" t="n">
-        <v>15444955.79</v>
+        <v>8214416.97</v>
       </c>
       <c r="AO3" t="n">
-        <v>820944051.22</v>
+        <v>704489946.26</v>
       </c>
       <c r="AP3" t="n">
-        <v>273024149.26</v>
+        <v>61905328.73</v>
       </c>
       <c r="AQ3" t="n">
-        <v>547919901.96</v>
+        <v>642584617.53</v>
       </c>
       <c r="AR3" t="n">
-        <v>199840.36</v>
+        <v>261750.62</v>
       </c>
       <c r="AS3" t="n">
-        <v>31136136.2</v>
+        <v>31899030.75</v>
       </c>
       <c r="AT3" t="n">
-        <v>31136136.2</v>
+        <v>31899030.75</v>
       </c>
       <c r="AU3" t="n">
-        <v>262767825</v>
+        <v>189200599.46</v>
       </c>
       <c r="AV3" t="n">
-        <v>-127575554.91</v>
+        <v>-117038974.04</v>
       </c>
       <c r="AW3" t="n">
-        <v>390343379.91</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+        <v>306239573.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>62292843.6</v>
+      </c>
       <c r="AY3" t="n">
-        <v>28579861.33</v>
+        <v>17866090.91</v>
       </c>
       <c r="AZ3" t="n">
-        <v>142539429.79</v>
+        <v>124126897.35</v>
       </c>
       <c r="BA3" t="n">
-        <v>219224088.79</v>
+        <v>101953741.64</v>
       </c>
       <c r="BB3" t="n">
-        <v>739467794.37</v>
+        <v>992181829.95</v>
       </c>
       <c r="BC3" t="n">
-        <v>45173755.72</v>
+        <v>7996547.63</v>
       </c>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
-        <v>2063351.85</v>
+        <v>4233036.67</v>
       </c>
       <c r="BF3" t="n">
-        <v>129265607.52</v>
+        <v>137160742.25</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>46855188.47</v>
+        <v>41487391.72</v>
       </c>
       <c r="BI3" t="n">
-        <v>45574972.74</v>
+        <v>49042755.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>36835446.31</v>
+        <v>46630595.52</v>
       </c>
       <c r="BK3" t="n">
-        <v>7248446.48</v>
+        <v>7137673.84</v>
       </c>
       <c r="BL3" t="n">
-        <v>155424049.82</v>
+        <v>143006910.5</v>
       </c>
       <c r="BM3" t="n">
-        <v>-5732866.52</v>
+        <v>-21791173.14</v>
       </c>
       <c r="BN3" t="n">
-        <v>161156916.34</v>
+        <v>164798083.64</v>
       </c>
       <c r="BO3" t="n">
-        <v>400292582.98</v>
+        <v>692646919.0599999</v>
       </c>
       <c r="BP3" t="n">
-        <v>314866336.32</v>
+        <v>550040201.89</v>
       </c>
       <c r="BQ3" t="n">
-        <v>85426246.66</v>
+        <v>142606717.17</v>
       </c>
       <c r="BR3" t="n">
-        <v>46595789.59</v>
+        <v>32271031.61</v>
       </c>
       <c r="BS3" t="n">
-        <v>38830457.07</v>
+        <v>110335685.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>577504854</v>
@@ -2111,40 +2107,40 @@
         <v>577504854</v>
       </c>
       <c r="D4" t="n">
-        <v>5339702.31</v>
+        <v>10873332.18</v>
       </c>
       <c r="E4" t="n">
-        <v>1469166030.48</v>
+        <v>1479531427.47</v>
       </c>
       <c r="F4" t="n">
-        <v>1503077830.63</v>
+        <v>1516675822.86</v>
       </c>
       <c r="G4" t="n">
-        <v>644139975.55</v>
+        <v>441901671.27</v>
       </c>
       <c r="H4" t="n">
-        <v>1469166030.48</v>
+        <v>1479531427.47</v>
       </c>
       <c r="I4" t="n">
-        <v>1327387.84</v>
+        <v>2644256.88</v>
       </c>
       <c r="J4" t="n">
-        <v>1501065061.23</v>
+        <v>1510667563.67</v>
       </c>
       <c r="K4" t="n">
-        <v>1501065061.23</v>
+        <v>1513672018.67</v>
       </c>
       <c r="L4" t="n">
-        <v>1552257591.29</v>
+        <v>1563102181.11</v>
       </c>
       <c r="M4" t="n">
-        <v>51192530.06</v>
+        <v>52434617.44</v>
       </c>
       <c r="N4" t="n">
-        <v>1501065061.23</v>
+        <v>1510667563.67</v>
       </c>
       <c r="O4" t="n">
-        <v>-62330758.73</v>
+        <v>-51872062.05</v>
       </c>
       <c r="P4" t="n">
         <v>870480939.47</v>
@@ -2156,162 +2152,164 @@
         <v>577504854</v>
       </c>
       <c r="S4" t="n">
-        <v>384296431.11</v>
+        <v>328590770.32</v>
       </c>
       <c r="T4" t="n">
-        <v>36254576.71</v>
+        <v>31024647.22</v>
       </c>
       <c r="U4" t="n">
-        <v>3027604.25</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
+        <v>8388369.95</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1650000</v>
+      </c>
       <c r="W4" t="n">
-        <v>219222.38</v>
+        <v>3226545.76</v>
       </c>
       <c r="X4" t="n">
-        <v>31680362.24</v>
+        <v>12111019.63</v>
       </c>
       <c r="Y4" t="n">
-        <v>1327387.84</v>
+        <v>5648711.88</v>
       </c>
       <c r="Z4" t="n">
-        <v>1327387.84</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
+        <v>2644256.88</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3004455</v>
+      </c>
       <c r="AB4" t="n">
-        <v>348041854.4</v>
+        <v>297566123.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>4090508.3</v>
+        <v>4275212.18</v>
       </c>
       <c r="AD4" t="n">
-        <v>4012314.47</v>
+        <v>5224620.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>2012769.4</v>
+        <v>3003804.19</v>
       </c>
       <c r="AF4" t="n">
-        <v>331116377.25</v>
+        <v>281375338.03</v>
       </c>
       <c r="AG4" t="n">
-        <v>76955174.40000001</v>
+        <v>36708620.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>22951473.67</v>
+        <v>8296307.17</v>
       </c>
       <c r="AI4" t="n">
-        <v>231209729.18</v>
+        <v>236370410.62</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1936554022.4</v>
+        <v>1891692951.43</v>
       </c>
       <c r="AK4" t="n">
-        <v>944372192.45</v>
+        <v>1152225157.06</v>
       </c>
       <c r="AL4" t="n">
-        <v>1932854.92</v>
+        <v>5056339.93</v>
       </c>
       <c r="AM4" t="n">
-        <v>8373593.47</v>
+        <v>16676008.56</v>
       </c>
       <c r="AN4" t="n">
-        <v>8214416.97</v>
+        <v>15444955.79</v>
       </c>
       <c r="AO4" t="n">
-        <v>704489946.26</v>
+        <v>820944051.22</v>
       </c>
       <c r="AP4" t="n">
-        <v>61905328.73</v>
+        <v>273024149.26</v>
       </c>
       <c r="AQ4" t="n">
-        <v>642584617.53</v>
+        <v>547919901.96</v>
       </c>
       <c r="AR4" t="n">
-        <v>261750.62</v>
+        <v>199840.36</v>
       </c>
       <c r="AS4" t="n">
-        <v>31899030.75</v>
+        <v>31136136.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>31899030.75</v>
+        <v>31136136.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>189200599.46</v>
+        <v>262767825</v>
       </c>
       <c r="AV4" t="n">
-        <v>-117038974.04</v>
+        <v>-127575554.91</v>
       </c>
       <c r="AW4" t="n">
-        <v>306239573.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>62292843.6</v>
-      </c>
+        <v>390343379.91</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>17866090.91</v>
+        <v>28579861.33</v>
       </c>
       <c r="AZ4" t="n">
-        <v>124126897.35</v>
+        <v>142539429.79</v>
       </c>
       <c r="BA4" t="n">
-        <v>101953741.64</v>
+        <v>219224088.79</v>
       </c>
       <c r="BB4" t="n">
-        <v>992181829.95</v>
+        <v>739467794.37</v>
       </c>
       <c r="BC4" t="n">
-        <v>7996547.63</v>
+        <v>45173755.72</v>
       </c>
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
-        <v>4233036.67</v>
+        <v>2063351.85</v>
       </c>
       <c r="BF4" t="n">
-        <v>137160742.25</v>
+        <v>129265607.52</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>41487391.72</v>
+        <v>46855188.47</v>
       </c>
       <c r="BI4" t="n">
-        <v>49042755.01</v>
+        <v>45574972.74</v>
       </c>
       <c r="BJ4" t="n">
-        <v>46630595.52</v>
+        <v>36835446.31</v>
       </c>
       <c r="BK4" t="n">
-        <v>7137673.84</v>
+        <v>7248446.48</v>
       </c>
       <c r="BL4" t="n">
-        <v>143006910.5</v>
+        <v>155424049.82</v>
       </c>
       <c r="BM4" t="n">
-        <v>-21791173.14</v>
+        <v>-5732866.52</v>
       </c>
       <c r="BN4" t="n">
-        <v>164798083.64</v>
+        <v>161156916.34</v>
       </c>
       <c r="BO4" t="n">
-        <v>692646919.0599999</v>
+        <v>400292582.98</v>
       </c>
       <c r="BP4" t="n">
-        <v>550040201.89</v>
+        <v>314866336.32</v>
       </c>
       <c r="BQ4" t="n">
-        <v>142606717.17</v>
+        <v>85426246.66</v>
       </c>
       <c r="BR4" t="n">
-        <v>32271031.61</v>
+        <v>46595789.59</v>
       </c>
       <c r="BS4" t="n">
-        <v>110335685.56</v>
+        <v>38830457.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>577504854</v>
@@ -2320,40 +2318,40 @@
         <v>577504854</v>
       </c>
       <c r="D5" t="n">
-        <v>8567861.630000001</v>
+        <v>6518126.54</v>
       </c>
       <c r="E5" t="n">
-        <v>1323557533.39</v>
+        <v>1451251195.93</v>
       </c>
       <c r="F5" t="n">
-        <v>1356556272.29</v>
+        <v>1486291088.47</v>
       </c>
       <c r="G5" t="n">
-        <v>607980141.99</v>
+        <v>320584113.02</v>
       </c>
       <c r="H5" t="n">
-        <v>1323557533.39</v>
+        <v>1451251195.93</v>
       </c>
       <c r="I5" t="n">
-        <v>3578802.32</v>
+        <v>177974.22</v>
       </c>
       <c r="J5" t="n">
-        <v>1356556272.29</v>
+        <v>1481783534.47</v>
       </c>
       <c r="K5" t="n">
-        <v>1356556272.29</v>
+        <v>1484188778.47</v>
       </c>
       <c r="L5" t="n">
-        <v>1404564493.35</v>
+        <v>1545000026.89</v>
       </c>
       <c r="M5" t="n">
-        <v>48008221.06</v>
+        <v>63216492.42</v>
       </c>
       <c r="N5" t="n">
-        <v>1356556272.29</v>
+        <v>1481783534.47</v>
       </c>
       <c r="O5" t="n">
-        <v>-206525100.98</v>
+        <v>-74170568.37</v>
       </c>
       <c r="P5" t="n">
         <v>870480939.47</v>
@@ -2365,157 +2363,159 @@
         <v>577504854</v>
       </c>
       <c r="S5" t="n">
-        <v>560587861.01</v>
+        <v>402605396.75</v>
       </c>
       <c r="T5" t="n">
-        <v>59367964.75</v>
+        <v>29762337.91</v>
       </c>
       <c r="U5" t="n">
-        <v>8694378.619999999</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
+        <v>8414035.960000001</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1650000</v>
+      </c>
       <c r="W5" t="n">
-        <v>261095.9</v>
+        <v>5077895.49</v>
       </c>
       <c r="X5" t="n">
-        <v>46833687.91</v>
+        <v>12037188.24</v>
       </c>
       <c r="Y5" t="n">
-        <v>3578802.32</v>
+        <v>2583218.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>3578802.32</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
+        <v>177974.22</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2405244</v>
+      </c>
       <c r="AB5" t="n">
-        <v>501219896.26</v>
+        <v>372843058.84</v>
       </c>
       <c r="AC5" t="n">
-        <v>7329208.15</v>
+        <v>11274582.29</v>
       </c>
       <c r="AD5" t="n">
-        <v>4989059.31</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
+        <v>3934908.32</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2102310</v>
+      </c>
       <c r="AF5" t="n">
-        <v>468732152.5</v>
+        <v>337569658.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>81110662.29000001</v>
+        <v>38912792.53</v>
       </c>
       <c r="AH5" t="n">
-        <v>8759974.140000001</v>
+        <v>11353330.38</v>
       </c>
       <c r="AI5" t="n">
-        <v>378861516.07</v>
+        <v>287303535.26</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1965152354.36</v>
+        <v>1947605423.64</v>
       </c>
       <c r="AK5" t="n">
-        <v>855952316.11</v>
+        <v>1254178251.78</v>
       </c>
       <c r="AL5" t="n">
-        <v>6930322.87</v>
+        <v>849847.24</v>
       </c>
       <c r="AM5" t="n">
-        <v>1234562.3</v>
+        <v>14633669.92</v>
       </c>
       <c r="AN5" t="n">
-        <v>15178492.15</v>
+        <v>16325761.58</v>
       </c>
       <c r="AO5" t="n">
-        <v>687169793.16</v>
+        <v>941785908.6900001</v>
       </c>
       <c r="AP5" t="n">
-        <v>30011671.23</v>
+        <v>482893150.55</v>
       </c>
       <c r="AQ5" t="n">
-        <v>657158121.9299999</v>
+        <v>458892758.14</v>
       </c>
       <c r="AR5" t="n">
-        <v>3533649.11</v>
+        <v>82244.77</v>
       </c>
       <c r="AS5" t="n">
-        <v>32998738.9</v>
+        <v>30532338.54</v>
       </c>
       <c r="AT5" t="n">
-        <v>32998738.9</v>
+        <v>30532338.54</v>
       </c>
       <c r="AU5" t="n">
-        <v>108906757.62</v>
+        <v>249968481.04</v>
       </c>
       <c r="AV5" t="n">
-        <v>-122798140.93</v>
+        <v>-121012061.14</v>
       </c>
       <c r="AW5" t="n">
-        <v>231704898.55</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>286359.26</v>
-      </c>
+        <v>370980542.18</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>23591194.67</v>
+        <v>29990239.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>105873602.98</v>
+        <v>125978795.42</v>
       </c>
       <c r="BA5" t="n">
-        <v>101953741.64</v>
+        <v>215011507.75</v>
       </c>
       <c r="BB5" t="n">
-        <v>1109200038.25</v>
+        <v>693427171.86</v>
       </c>
       <c r="BC5" t="n">
-        <v>263840614</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>23458626.11</v>
-      </c>
+        <v>77280110.70999999</v>
+      </c>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
-        <v>7688880.78</v>
+        <v>1662545.88</v>
       </c>
       <c r="BF5" t="n">
-        <v>140298141.54</v>
+        <v>139278999.81</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>17658563.15</v>
+        <v>56996654.38</v>
       </c>
       <c r="BI5" t="n">
-        <v>39437015.51</v>
+        <v>48741070.27</v>
       </c>
       <c r="BJ5" t="n">
-        <v>83202562.88</v>
+        <v>33541275.16</v>
       </c>
       <c r="BK5" t="n">
-        <v>11236877.54</v>
+        <v>26733639.97</v>
       </c>
       <c r="BL5" t="n">
-        <v>225519002.53</v>
+        <v>186622613.68</v>
       </c>
       <c r="BM5" t="n">
-        <v>-41592316.05</v>
+        <v>-6682506.89</v>
       </c>
       <c r="BN5" t="n">
-        <v>267111318.58</v>
+        <v>193305120.57</v>
       </c>
       <c r="BO5" t="n">
-        <v>437157895.75</v>
+        <v>261849261.81</v>
       </c>
       <c r="BP5" t="n">
-        <v>300311075.1</v>
+        <v>135692546.92</v>
       </c>
       <c r="BQ5" t="n">
-        <v>136846820.65</v>
+        <v>126156714.89</v>
       </c>
       <c r="BR5" t="n">
-        <v>43783872.28</v>
+        <v>30958920.4</v>
       </c>
       <c r="BS5" t="n">
-        <v>93062948.37</v>
+        <v>95197794.48999999</v>
       </c>
     </row>
   </sheetData>
@@ -2771,578 +2771,578 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>48551577.73</v>
+        <v>27976303.01</v>
       </c>
       <c r="C2" t="n">
-        <v>-6909147.21</v>
+        <v>-6462300</v>
       </c>
       <c r="D2" t="n">
-        <v>5400000</v>
+        <v>6462300</v>
       </c>
       <c r="E2" t="n">
-        <v>-35012495.07</v>
+        <v>-18621656.12</v>
       </c>
       <c r="F2" t="n">
-        <v>86783790.81</v>
+        <v>73275973.53</v>
       </c>
       <c r="G2" t="n">
-        <v>30212118.93</v>
+        <v>132550665.37</v>
       </c>
       <c r="H2" t="n">
-        <v>2600479.01</v>
+        <v>-1084000.03</v>
       </c>
       <c r="I2" t="n">
-        <v>53971192.87</v>
+        <v>-58190691.81</v>
       </c>
       <c r="J2" t="n">
-        <v>9217800.91</v>
+        <v>-2338411.21</v>
       </c>
       <c r="K2" t="n">
-        <v>12824721.34</v>
+        <v>-415012.91</v>
       </c>
       <c r="L2" t="n">
-        <v>-639213.22</v>
+        <v>-336998.3</v>
       </c>
       <c r="M2" t="n">
-        <v>-1509147.21</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-1509147.21</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-6909147.21</v>
+        <v>-6462300</v>
       </c>
       <c r="P2" t="n">
-        <v>5400000</v>
+        <v>6462300</v>
       </c>
       <c r="Q2" t="n">
-        <v>-38810680.84</v>
+        <v>-102450239.73</v>
       </c>
       <c r="R2" t="n">
-        <v>100000</v>
+        <v>51920720.8</v>
       </c>
       <c r="S2" t="n">
-        <v>-4171990.77</v>
+        <v>-141596490.58</v>
       </c>
       <c r="T2" t="n">
-        <v>1234980653.12</v>
+        <v>2748194884.42</v>
       </c>
       <c r="U2" t="n">
-        <v>-1239152643.89</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>-2889791375</v>
+      </c>
+      <c r="V2" t="n">
+        <v>4836656.17</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4836656.17</v>
+      </c>
       <c r="X2" t="n">
-        <v>-34738690.07</v>
+        <v>-17611126.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>273805</v>
+        <v>1010530</v>
       </c>
       <c r="Z2" t="n">
-        <v>-35012495.07</v>
+        <v>-18621656.12</v>
       </c>
       <c r="AA2" t="n">
-        <v>83564072.8</v>
+        <v>46597959.13</v>
       </c>
       <c r="AB2" t="n">
-        <v>23851630.47</v>
+        <v>18623124.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>-954637.1800000001</v>
+        <v>1463504.66</v>
       </c>
       <c r="AD2" t="n">
-        <v>105604522.98</v>
+        <v>112751411.87</v>
       </c>
       <c r="AE2" t="n">
-        <v>-19541560.08</v>
+        <v>-54126828.76</v>
       </c>
       <c r="AF2" t="n">
-        <v>-61256695.25</v>
+        <v>-41464963.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>1006891.98</v>
+        <v>3149844.75</v>
       </c>
       <c r="AH2" t="n">
-        <v>24545705.41</v>
+        <v>18670053.52</v>
       </c>
       <c r="AI2" t="n">
-        <v>995307.09</v>
+        <v>1245233.94</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23550398.32</v>
+        <v>17424819.58</v>
       </c>
       <c r="AK2" t="n">
-        <v>33410483.96</v>
+        <v>-35542937.84</v>
       </c>
       <c r="AL2" t="n">
-        <v>536816.01</v>
+        <v>654450.39</v>
       </c>
       <c r="AM2" t="n">
-        <v>-10796173.49</v>
+        <v>-107250693.62</v>
       </c>
       <c r="AN2" t="n">
-        <v>83564072.8</v>
+        <v>46597959.13</v>
       </c>
       <c r="AO2" t="n">
-        <v>31080256.43</v>
+        <v>31427275.93</v>
       </c>
       <c r="AP2" t="n">
-        <v>-886339018.23</v>
+        <v>-916931428.15</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-370321802.89</v>
+        <v>-60689702.07</v>
       </c>
       <c r="AR2" t="n">
-        <v>-138108625.31</v>
+        <v>-152557343.52</v>
       </c>
       <c r="AS2" t="n">
-        <v>-377908590.03</v>
+        <v>-703684382.5599999</v>
       </c>
       <c r="AT2" t="n">
-        <v>938822834.6</v>
+        <v>932102111.35</v>
       </c>
       <c r="AU2" t="n">
-        <v>375304553.12</v>
+        <v>10208193.02</v>
       </c>
       <c r="AV2" t="n">
-        <v>563518281.48</v>
+        <v>921893918.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-66006895.26</v>
+        <v>-80680917.48</v>
       </c>
       <c r="C3" t="n">
-        <v>-5598697.1</v>
+        <v>-5288860.1</v>
       </c>
       <c r="D3" t="n">
-        <v>9581350.58</v>
+        <v>7075972</v>
       </c>
       <c r="E3" t="n">
-        <v>-104431874.42</v>
+        <v>-78559708.83</v>
       </c>
       <c r="F3" t="n">
-        <v>30212118.93</v>
+        <v>102037174.89</v>
       </c>
       <c r="G3" t="n">
-        <v>102037174.89</v>
+        <v>73275973.53</v>
       </c>
       <c r="H3" t="n">
-        <v>-866725.86</v>
+        <v>4746562.9</v>
       </c>
       <c r="I3" t="n">
-        <v>-70958330.09999999</v>
+        <v>24014638.46</v>
       </c>
       <c r="J3" t="n">
-        <v>-17683702.5</v>
+        <v>8149687.97</v>
       </c>
       <c r="K3" t="n">
-        <v>-20453836.71</v>
+        <v>7314988.87</v>
       </c>
       <c r="L3" t="n">
-        <v>-194919.27</v>
+        <v>-104412.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3982653.48</v>
+        <v>1787111.9</v>
       </c>
       <c r="N3" t="n">
-        <v>3982653.48</v>
+        <v>1787111.9</v>
       </c>
       <c r="O3" t="n">
-        <v>-5598697.1</v>
+        <v>-5288860.1</v>
       </c>
       <c r="P3" t="n">
-        <v>9581350.58</v>
+        <v>7075972</v>
       </c>
       <c r="Q3" t="n">
-        <v>-91699606.76000001</v>
+        <v>17986159.14</v>
       </c>
       <c r="R3" t="n">
-        <v>4620000</v>
+        <v>22537072.98</v>
       </c>
       <c r="S3" t="n">
-        <v>7279651.54</v>
+        <v>-5272025.04</v>
       </c>
       <c r="T3" t="n">
-        <v>1797033308.72</v>
+        <v>3041296974.96</v>
       </c>
       <c r="U3" t="n">
-        <v>-1789753657.18</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
+        <v>-3046569000</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>-103599259.3</v>
+        <v>721111.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>832615.12</v>
+        <v>79280820.03</v>
       </c>
       <c r="Z3" t="n">
-        <v>-104431874.42</v>
+        <v>-78559708.83</v>
       </c>
       <c r="AA3" t="n">
-        <v>38424979.16</v>
+        <v>-2121208.65</v>
       </c>
       <c r="AB3" t="n">
-        <v>-48692966.54</v>
+        <v>-78516997.69</v>
       </c>
       <c r="AC3" t="n">
-        <v>-26799881.43</v>
+        <v>-8358176.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>-35200280.87</v>
+        <v>-145823821.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>4819401.72</v>
+        <v>-5558303.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>8487794.039999999</v>
+        <v>81223303.23999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>4887745.48</v>
+        <v>-3404513.01</v>
       </c>
       <c r="AH3" t="n">
-        <v>15867382.19</v>
+        <v>15974826.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>1061007.76</v>
+        <v>1151241.17</v>
       </c>
       <c r="AJ3" t="n">
-        <v>14806374.43</v>
+        <v>14823585.33</v>
       </c>
       <c r="AK3" t="n">
-        <v>36716413.37</v>
+        <v>4121901.66</v>
       </c>
       <c r="AL3" t="n">
-        <v>60313.3</v>
+        <v>-102728217.87</v>
       </c>
       <c r="AM3" t="n">
-        <v>18601764.68</v>
+        <v>148245061.15</v>
       </c>
       <c r="AN3" t="n">
-        <v>38424979.16</v>
+        <v>-2121208.65</v>
       </c>
       <c r="AO3" t="n">
-        <v>5126729.8</v>
+        <v>16772216.27</v>
       </c>
       <c r="AP3" t="n">
-        <v>-548526040.67</v>
+        <v>-776833696.58</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-49612925.95</v>
+        <v>-51700358.92</v>
       </c>
       <c r="AR3" t="n">
-        <v>-139305358.5</v>
+        <v>-136910266.97</v>
       </c>
       <c r="AS3" t="n">
-        <v>-359607756.22</v>
+        <v>-588223070.6900001</v>
       </c>
       <c r="AT3" t="n">
-        <v>581824290.03</v>
+        <v>757940271.66</v>
       </c>
       <c r="AU3" t="n">
-        <v>10290372.08</v>
+        <v>36608619.55</v>
       </c>
       <c r="AV3" t="n">
-        <v>571533917.95</v>
+        <v>721331652.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-80680917.48</v>
+        <v>-66006895.26</v>
       </c>
       <c r="C4" t="n">
-        <v>-5288860.1</v>
+        <v>-5598697.1</v>
       </c>
       <c r="D4" t="n">
-        <v>7075972</v>
+        <v>9581350.58</v>
       </c>
       <c r="E4" t="n">
-        <v>-78559708.83</v>
+        <v>-104431874.42</v>
       </c>
       <c r="F4" t="n">
+        <v>30212118.93</v>
+      </c>
+      <c r="G4" t="n">
         <v>102037174.89</v>
       </c>
-      <c r="G4" t="n">
-        <v>73275973.53</v>
-      </c>
       <c r="H4" t="n">
-        <v>4746562.9</v>
+        <v>-866725.86</v>
       </c>
       <c r="I4" t="n">
-        <v>24014638.46</v>
+        <v>-70958330.09999999</v>
       </c>
       <c r="J4" t="n">
-        <v>8149687.97</v>
+        <v>-17683702.5</v>
       </c>
       <c r="K4" t="n">
-        <v>7314988.87</v>
+        <v>-20453836.71</v>
       </c>
       <c r="L4" t="n">
-        <v>-104412.8</v>
+        <v>-194919.27</v>
       </c>
       <c r="M4" t="n">
-        <v>1787111.9</v>
+        <v>3982653.48</v>
       </c>
       <c r="N4" t="n">
-        <v>1787111.9</v>
+        <v>3982653.48</v>
       </c>
       <c r="O4" t="n">
-        <v>-5288860.1</v>
+        <v>-5598697.1</v>
       </c>
       <c r="P4" t="n">
-        <v>7075972</v>
+        <v>9581350.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>17986159.14</v>
+        <v>-91699606.76000001</v>
       </c>
       <c r="R4" t="n">
-        <v>22537072.98</v>
+        <v>4620000</v>
       </c>
       <c r="S4" t="n">
-        <v>-5272025.04</v>
+        <v>7279651.54</v>
       </c>
       <c r="T4" t="n">
-        <v>3041296974.96</v>
+        <v>1797033308.72</v>
       </c>
       <c r="U4" t="n">
-        <v>-3046569000</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+        <v>-1789753657.18</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
       <c r="X4" t="n">
-        <v>721111.2</v>
+        <v>-103599259.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>79280820.03</v>
+        <v>832615.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>-78559708.83</v>
+        <v>-104431874.42</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2121208.65</v>
+        <v>38424979.16</v>
       </c>
       <c r="AB4" t="n">
-        <v>-78516997.69</v>
+        <v>-48692966.54</v>
       </c>
       <c r="AC4" t="n">
-        <v>-8358176.6</v>
+        <v>-26799881.43</v>
       </c>
       <c r="AD4" t="n">
-        <v>-145823821.28</v>
+        <v>-35200280.87</v>
       </c>
       <c r="AE4" t="n">
-        <v>-5558303.05</v>
+        <v>4819401.72</v>
       </c>
       <c r="AF4" t="n">
-        <v>81223303.23999999</v>
+        <v>8487794.039999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3404513.01</v>
+        <v>4887745.48</v>
       </c>
       <c r="AH4" t="n">
-        <v>15974826.5</v>
+        <v>15867382.19</v>
       </c>
       <c r="AI4" t="n">
-        <v>1151241.17</v>
+        <v>1061007.76</v>
       </c>
       <c r="AJ4" t="n">
-        <v>14823585.33</v>
+        <v>14806374.43</v>
       </c>
       <c r="AK4" t="n">
-        <v>4121901.66</v>
+        <v>36716413.37</v>
       </c>
       <c r="AL4" t="n">
-        <v>-102728217.87</v>
+        <v>60313.3</v>
       </c>
       <c r="AM4" t="n">
-        <v>148245061.15</v>
+        <v>18601764.68</v>
       </c>
       <c r="AN4" t="n">
-        <v>-2121208.65</v>
+        <v>38424979.16</v>
       </c>
       <c r="AO4" t="n">
-        <v>16772216.27</v>
+        <v>5126729.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>-776833696.58</v>
+        <v>-548526040.67</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-51700358.92</v>
+        <v>-49612925.95</v>
       </c>
       <c r="AR4" t="n">
-        <v>-136910266.97</v>
+        <v>-139305358.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>-588223070.6900001</v>
+        <v>-359607756.22</v>
       </c>
       <c r="AT4" t="n">
-        <v>757940271.66</v>
+        <v>581824290.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>36608619.55</v>
+        <v>10290372.08</v>
       </c>
       <c r="AV4" t="n">
-        <v>721331652.11</v>
+        <v>571533917.95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>27976303.01</v>
+        <v>48551577.73</v>
       </c>
       <c r="C5" t="n">
-        <v>-6462300</v>
+        <v>-6909147.21</v>
       </c>
       <c r="D5" t="n">
-        <v>6462300</v>
+        <v>5400000</v>
       </c>
       <c r="E5" t="n">
-        <v>-18621656.12</v>
+        <v>-35012495.07</v>
       </c>
       <c r="F5" t="n">
-        <v>73275973.53</v>
+        <v>86783790.81</v>
       </c>
       <c r="G5" t="n">
-        <v>132550665.37</v>
+        <v>30212118.93</v>
       </c>
       <c r="H5" t="n">
-        <v>-1084000.03</v>
+        <v>2600479.01</v>
       </c>
       <c r="I5" t="n">
-        <v>-58190691.81</v>
+        <v>53971192.87</v>
       </c>
       <c r="J5" t="n">
-        <v>-2338411.21</v>
+        <v>9217800.91</v>
       </c>
       <c r="K5" t="n">
-        <v>-415012.91</v>
+        <v>12824721.34</v>
       </c>
       <c r="L5" t="n">
-        <v>-336998.3</v>
+        <v>-639213.22</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1509147.21</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1509147.21</v>
       </c>
       <c r="O5" t="n">
-        <v>-6462300</v>
+        <v>-6909147.21</v>
       </c>
       <c r="P5" t="n">
-        <v>6462300</v>
+        <v>5400000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-102450239.73</v>
+        <v>-38810680.84</v>
       </c>
       <c r="R5" t="n">
-        <v>51920720.8</v>
+        <v>100000</v>
       </c>
       <c r="S5" t="n">
-        <v>-141596490.58</v>
+        <v>-4171990.77</v>
       </c>
       <c r="T5" t="n">
-        <v>2748194884.42</v>
+        <v>1234980653.12</v>
       </c>
       <c r="U5" t="n">
-        <v>-2889791375</v>
-      </c>
-      <c r="V5" t="n">
-        <v>4836656.17</v>
-      </c>
-      <c r="W5" t="n">
-        <v>4836656.17</v>
-      </c>
+        <v>-1239152643.89</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-17611126.12</v>
+        <v>-34738690.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1010530</v>
+        <v>273805</v>
       </c>
       <c r="Z5" t="n">
-        <v>-18621656.12</v>
+        <v>-35012495.07</v>
       </c>
       <c r="AA5" t="n">
-        <v>46597959.13</v>
+        <v>83564072.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>18623124.17</v>
+        <v>23851630.47</v>
       </c>
       <c r="AC5" t="n">
-        <v>1463504.66</v>
+        <v>-954637.1800000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>112751411.87</v>
+        <v>105604522.98</v>
       </c>
       <c r="AE5" t="n">
-        <v>-54126828.76</v>
+        <v>-19541560.08</v>
       </c>
       <c r="AF5" t="n">
-        <v>-41464963.6</v>
+        <v>-61256695.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>3149844.75</v>
+        <v>1006891.98</v>
       </c>
       <c r="AH5" t="n">
-        <v>18670053.52</v>
+        <v>24545705.41</v>
       </c>
       <c r="AI5" t="n">
-        <v>1245233.94</v>
+        <v>995307.09</v>
       </c>
       <c r="AJ5" t="n">
-        <v>17424819.58</v>
+        <v>23550398.32</v>
       </c>
       <c r="AK5" t="n">
-        <v>-35542937.84</v>
+        <v>33410483.96</v>
       </c>
       <c r="AL5" t="n">
-        <v>654450.39</v>
+        <v>536816.01</v>
       </c>
       <c r="AM5" t="n">
-        <v>-107250693.62</v>
+        <v>-10796173.49</v>
       </c>
       <c r="AN5" t="n">
-        <v>46597959.13</v>
+        <v>83564072.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>31427275.93</v>
+        <v>31080256.43</v>
       </c>
       <c r="AP5" t="n">
-        <v>-916931428.15</v>
+        <v>-886339018.23</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-60689702.07</v>
+        <v>-370321802.89</v>
       </c>
       <c r="AR5" t="n">
-        <v>-152557343.52</v>
+        <v>-138108625.31</v>
       </c>
       <c r="AS5" t="n">
-        <v>-703684382.5599999</v>
+        <v>-377908590.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>932102111.35</v>
+        <v>938822834.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>10208193.02</v>
+        <v>375304553.12</v>
       </c>
       <c r="AV5" t="n">
-        <v>921893918.33</v>
+        <v>563518281.48</v>
       </c>
     </row>
   </sheetData>
@@ -3897,192 +3897,192 @@
       </c>
       <c r="DD1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
       <c r="DH1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>prevName</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>nameChangeDate</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EP1" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Ms. Yamei  Chen', 'age': 50, 'title': 'Founder &amp; Chairman', 'yearBorn': 1975, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xin  Qiao', 'age': 62, 'title': 'Founder, Director &amp; CEO', 'yearBorn': 1963, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Suhua  Yuan', 'age': 46, 'title': 'Secretary of the Board of Directors', 'yearBorn': 1979, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Jie Heng  Pan', 'title': 'Accounting Supervisor', 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Ms. Yamei  Chen', 'age': 50, 'title': 'Founder &amp; Chairman', 'yearBorn': 1975, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xin  Qiao', 'age': 62, 'title': 'Founder, Director &amp; CEO', 'yearBorn': 1963, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Jie Heng  Pan', 'title': 'Accounting Supervisor', 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -4177,34 +4177,34 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>8.970000000000001</v>
+        <v>10.55</v>
       </c>
       <c r="T2" t="n">
-        <v>8.699999999999999</v>
+        <v>10.34</v>
       </c>
       <c r="U2" t="n">
-        <v>8.42</v>
+        <v>10.48</v>
       </c>
       <c r="V2" t="n">
-        <v>8.94</v>
+        <v>11.09</v>
       </c>
       <c r="W2" t="n">
-        <v>8.970000000000001</v>
+        <v>10.55</v>
       </c>
       <c r="X2" t="n">
-        <v>8.699999999999999</v>
+        <v>10.34</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.42</v>
+        <v>10.48</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.94</v>
+        <v>11.09</v>
       </c>
       <c r="AA2" t="n">
         <v>0.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.59</v>
+        <v>0.46</v>
       </c>
       <c r="AC2" t="n">
         <v>1779753600</v>
@@ -4213,31 +4213,31 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.629</v>
+        <v>0.605</v>
       </c>
       <c r="AF2" t="n">
-        <v>121.28571</v>
+        <v>156.42857</v>
       </c>
       <c r="AG2" t="n">
-        <v>30321557</v>
+        <v>91924021</v>
       </c>
       <c r="AH2" t="n">
-        <v>30321557</v>
+        <v>91924021</v>
       </c>
       <c r="AI2" t="n">
-        <v>15362497</v>
+        <v>30239244</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23508518</v>
+        <v>88881606</v>
       </c>
       <c r="AK2" t="n">
-        <v>23508518</v>
+        <v>88881606</v>
       </c>
       <c r="AL2" t="n">
-        <v>8.49</v>
+        <v>10.95</v>
       </c>
       <c r="AM2" t="n">
-        <v>8.5</v>
+        <v>10.96</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -4246,16 +4246,16 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>4903015936</v>
+        <v>6323677696</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4903016210</v>
+        <v>6092676209</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.48</v>
+        <v>7.72</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.5</v>
+        <v>11.87</v>
       </c>
       <c r="AT2" t="n">
         <v>25.97</v>
@@ -4264,19 +4264,19 @@
         <v>1.68566</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.851371</v>
+        <v>8.836574000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.358599999999999</v>
+        <v>8.897399999999999</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.779999999999999</v>
+        <v>8.876749999999999</v>
       </c>
       <c r="AY2" t="n">
         <v>0.05</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.005574136</v>
+        <v>0.0047393367</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -4287,13 +4287,13 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>4836476416</v>
+        <v>6257138176</v>
       </c>
       <c r="BD2" t="n">
         <v>0.060399998</v>
       </c>
       <c r="BE2" t="n">
-        <v>336113600</v>
+        <v>336107825</v>
       </c>
       <c r="BF2" t="n">
         <v>577504854</v>
@@ -4311,7 +4311,7 @@
         <v>2.662</v>
       </c>
       <c r="BK2" t="n">
-        <v>3.1893313</v>
+        <v>4.1134486</v>
       </c>
       <c r="BL2" t="n">
         <v>1767139200</v>
@@ -4340,16 +4340,16 @@
         <v>1367798400</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.758</v>
+        <v>8.744</v>
       </c>
       <c r="BU2" t="n">
-        <v>73.206</v>
+        <v>94.709</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.12301588</v>
+        <v>0.23971796</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="BX2" t="n">
         <v>0.05</v>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="CA2" t="n">
-        <v>8.49</v>
+        <v>10.95</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
@@ -4465,147 +4465,147 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DD2" t="n">
-        <v>-5.3511763</v>
+      <c r="DD2" t="b">
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="DF2" t="b">
+        <v>1181698200000</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>3.7914655</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>1782111843</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>finmb_34556603</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DP2" t="b">
         <v>0</v>
       </c>
-      <c r="DG2" t="n">
-        <v>1181698200000</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>-0.4800005</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>8.42 - 8.94</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>SHENZHEN SEA STAR TECHNOLOGY CO</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Shenzhen Sea Star Technology Co.,Ltd</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.39999962</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>10.48 - 11.09</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
         <is>
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="DK2" t="n">
-        <v>15362497</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>1.0099998</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.13502671</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>7.48 - 10.5</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>-2.0100002</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.19142859</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>12.301588</v>
-      </c>
-      <c r="DR2" t="n">
+      <c r="DW2" t="n">
+        <v>30239244</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.4183938</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>7.72 - 11.87</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
+        <v>-0.9200001</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.077506326</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>23.971796</v>
+      </c>
+      <c r="ED2" t="n">
         <v>1619521140</v>
       </c>
-      <c r="DS2" t="n">
+      <c r="EE2" t="n">
         <v>1619521140</v>
       </c>
-      <c r="DT2" t="n">
+      <c r="EF2" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DU2" t="n">
-        <v>0.13140011</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0.015720349</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.28999996</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.03302961</v>
-      </c>
-      <c r="DY2" t="n">
+      <c r="EG2" t="n">
+        <v>2.0526</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>0.2306966</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>2.0732498</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>0.23355956</v>
+      </c>
+      <c r="EK2" t="n">
         <v>15</v>
       </c>
-      <c r="DZ2" t="n">
+      <c r="EL2" t="n">
         <v>15</v>
       </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EM2" t="inlineStr">
         <is>
           <t>Shen Zhen Mindata Holding Co., Ltd</t>
         </is>
       </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="EC2" t="b">
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="EO2" t="b">
         <v>0</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>SHENZHEN SEA STAR TECHNOLOGY CO</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>Shenzhen Sea Star Technology Co.,Ltd</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EG2" t="n">
-        <v>1780038282</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>finmb_34556603</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="EL2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="EN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
       </c>
       <c r="EP2" t="inlineStr"/>
     </row>
